--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/NEW_JERSEY_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/NEW_JERSEY_2024.xlsx
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C221">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C328">
